--- a/data/trans_orig/Q5409A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023 (tasa de respuesta: 96,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,47 +3719,47 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4276</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1417</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>39690</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>40167</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>39328</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>67415</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>99871</t>
+          <t>98838</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>120020</t>
+          <t>120010</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>32484</t>
+          <t>32848</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>29980</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>662</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>977</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>408</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>408</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,22 +1222,22 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>58,31%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>74,96%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>641</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>641</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>574</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>689</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>958</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,22 +3759,22 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>508</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39690</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>43419</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -4396,67 +4396,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>6944</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>2182</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>5249</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>61565</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>61565</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>61565</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>36069</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>75857</t>
+          <t>82637</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>118706</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>98838</t>
+          <t>106932</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>120010</t>
+          <t>129046</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>41706</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>65428</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>65428</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>65428</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>128877</t>
+          <t>142392</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>128877</t>
+          <t>142392</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>128877</t>
+          <t>142392</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>194305</t>
+          <t>212948</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>194305</t>
+          <t>212948</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>194305</t>
+          <t>212948</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
